--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5302-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5302-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6264910-9CE9-4E1B-A378-6D565AC57D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDFDA812-0D35-4AA4-93DB-E3F51AC31FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E3DECA9D-127F-4755-90F7-7F1D70E66A2A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C8A2F478-AF1A-475A-85A2-FDD4EA697898}"/>
   </bookViews>
   <sheets>
     <sheet name="5302-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1442,25 +1442,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201F9C74-BFC2-40B4-9A4A-FAF2C0969627}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAE1D410-129C-4C4D-BD2E-9471D295CA47}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1494,7 +1492,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1530,7 +1528,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1582,7 +1580,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1650,7 +1648,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1722,7 +1720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1794,7 +1792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1866,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1938,7 +1936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2010,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2082,7 +2080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2154,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2226,7 +2224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2298,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2370,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2442,7 +2440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2514,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2586,7 +2584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2658,7 +2656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2730,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2802,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2874,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2946,7 +2944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3018,7 +3016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3090,7 +3088,7 @@
         <v>5.67</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3162,7 +3160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3234,7 +3232,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3306,7 +3304,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3378,7 +3376,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3450,7 +3448,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3522,7 +3520,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3594,7 +3592,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3666,7 +3664,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3738,7 +3736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3810,7 +3808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3882,7 +3880,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -3954,7 +3952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4026,7 +4024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1991</v>
       </c>
@@ -4098,7 +4096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1990</v>
       </c>
@@ -4170,7 +4168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1988</v>
       </c>
@@ -4242,7 +4240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="34">
         <v>1987</v>
       </c>
@@ -4314,7 +4312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36" t="s">
         <v>39</v>
       </c>
